--- a/StructureDefinition-Fordjupad-analys.xlsx
+++ b/StructureDefinition-Fordjupad-analys.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:41:45+00:00</t>
+    <t>2026-09-18T09:59:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Fordjupad-analys.xlsx
+++ b/StructureDefinition-Fordjupad-analys.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T09:59:15+00:00</t>
+    <t>2026-09-18T10:29:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,12 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Supporting logical model generated from gloo4.xmi (source class: Fördjupad analys).</t>
+    <t>Ytterligare analys föranledd av specifikt analysresultat. 
+2018-03-14: Vi stryker denna i begreppsmodellen, det löser sig i informationsmodellen. 
+Vad är skillnad mellan fördjupad analys och konfirmationsanalys som de pratade om på mötet? Är det samma? 
+2018-03-09: Jonas Svanberg:   
+För mig oklart begrepp. Möjligen kan man mena ”analys/undersökning som normalt inte utförs i aktuell situation”. För mig är det bara en ytterligare Fyndegenskap (8.4).  
+Eller avses ”analys som utförs pga. resultatet i beställd analys, och som inte är beställd från början”? Och behövs för att hantera den situationen?</t>
   </si>
   <si>
     <t>Purpose</t>
